--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -7595,7 +7595,7 @@
         <v>102234570</v>
       </c>
       <c r="B63" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -7595,7 +7595,7 @@
         <v>102234570</v>
       </c>
       <c r="B63" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -7595,7 +7595,7 @@
         <v>102234570</v>
       </c>
       <c r="B63" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -7595,7 +7595,7 @@
         <v>102234570</v>
       </c>
       <c r="B63" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -7595,7 +7595,7 @@
         <v>102234570</v>
       </c>
       <c r="B63" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -7595,7 +7595,7 @@
         <v>102234570</v>
       </c>
       <c r="B63" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -7595,7 +7595,7 @@
         <v>102234570</v>
       </c>
       <c r="B63" t="n">
-        <v>99027</v>
+        <v>99032</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102233679</v>
+        <v>102233567</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,12 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -726,14 +716,14 @@
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skoludden, Gammelstilla, Hofors , Gstr</t>
+          <t>Hofors Skoludden Gammelstilla , Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590253.0723766009</v>
+        <v>590292</v>
       </c>
       <c r="R2" t="n">
-        <v>6701117.902228818</v>
+        <v>6701082</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -775,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,27 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102233902</v>
+        <v>102233679</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -853,14 +838,14 @@
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skoludden, Gammelstilla, Hofors, Gstr</t>
+          <t>Skoludden, Gammelstilla, Hofors , Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590284.6638333438</v>
+        <v>590253</v>
       </c>
       <c r="R3" t="n">
-        <v>6701140.41796702</v>
+        <v>6701118</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,15 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102233961</v>
+        <v>102233770</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,12 +944,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -979,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590256.5232385846</v>
+        <v>590261</v>
       </c>
       <c r="R4" t="n">
-        <v>6701138.235578407</v>
+        <v>6701139</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,15 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102234449</v>
+        <v>102233902</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1061,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1106,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590274.0138760417</v>
+        <v>590284</v>
       </c>
       <c r="R5" t="n">
-        <v>6701349.53396643</v>
+        <v>6701140</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1151,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,15 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102234626</v>
+        <v>102233961</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,25 +1183,25 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammelstillavägen, Hofors Skoludden , Gstr</t>
+          <t>Hofors Skoludden Gammelstilla , Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590246.3323505798</v>
+        <v>590257</v>
       </c>
       <c r="R6" t="n">
-        <v>6701348.844552399</v>
+        <v>6701138</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1263,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,15 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102233567</v>
+        <v>102234449</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1300,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1346,14 +1316,14 @@
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hofors Skoludden Gammelstilla , Gstr</t>
+          <t>Skoludden, Gammelstilla, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590292.5533593514</v>
+        <v>590275</v>
       </c>
       <c r="R7" t="n">
-        <v>6701081.847303319</v>
+        <v>6701349</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1385,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1395,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,27 +1380,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102233770</v>
+        <v>102234570</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,25 +1422,31 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hofors Skoludden Gammelstilla , Gstr</t>
+          <t>Gammelstillavägen, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590260.4533911288</v>
+        <v>590266</v>
       </c>
       <c r="R8" t="n">
-        <v>6701139.321126358</v>
+        <v>6701345</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1507,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1517,7 +1488,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,33 +1497,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>marianne johansson</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104520902</v>
+        <v>102234626</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,20 +1544,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skoludden Gammelstilla, Gstr</t>
+          <t>Gammelstillavägen, Hofors Skoludden , Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590251.1280053807</v>
+        <v>590246</v>
       </c>
       <c r="R9" t="n">
-        <v>6701354.889682747</v>
+        <v>6701349</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1614,22 +1591,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,27 +1621,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>marianne johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104520918</v>
+        <v>104520880</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590278.3572074606</v>
+        <v>590230</v>
       </c>
       <c r="R10" t="n">
-        <v>6701393.590945128</v>
+        <v>6701158</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1729,19 +1701,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,15 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104520883</v>
+        <v>104520881</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590227.5688350502</v>
+        <v>590164</v>
       </c>
       <c r="R11" t="n">
-        <v>6701148.87291859</v>
+        <v>6701220</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,19 +1798,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,15 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104520916</v>
+        <v>104520882</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590270.2560471552</v>
+        <v>590239</v>
       </c>
       <c r="R12" t="n">
-        <v>6701341.53940316</v>
+        <v>6701147</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,19 +1895,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,15 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104520920</v>
+        <v>104520883</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,10 +1959,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590277.7005102532</v>
+        <v>590227</v>
       </c>
       <c r="R13" t="n">
-        <v>6701380.241864207</v>
+        <v>6701149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,19 +1992,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2104,15 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104520925</v>
+        <v>104520884</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,10 +2056,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590287.8854916126</v>
+        <v>590176</v>
       </c>
       <c r="R14" t="n">
-        <v>6701110.373976417</v>
+        <v>6701281</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2177,19 +2089,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,15 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104520911</v>
+        <v>104520885</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590320.2625999645</v>
+        <v>590172</v>
       </c>
       <c r="R15" t="n">
-        <v>6701399.079308663</v>
+        <v>6701299</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,19 +2186,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2328,15 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104520899</v>
+        <v>104520886</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,10 +2250,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590266.1742569678</v>
+        <v>590159</v>
       </c>
       <c r="R16" t="n">
-        <v>6701406.126350956</v>
+        <v>6701234</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,19 +2283,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,15 +2312,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104520892</v>
+        <v>104520887</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590267.1918290092</v>
+        <v>590237</v>
       </c>
       <c r="R17" t="n">
-        <v>6701345.413563881</v>
+        <v>6701171</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2513,19 +2380,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,15 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104520939</v>
+        <v>104520888</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590284.8851238606</v>
+        <v>590253</v>
       </c>
       <c r="R18" t="n">
-        <v>6701131.534384439</v>
+        <v>6701331</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2625,19 +2477,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,15 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104520880</v>
+        <v>104520889</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590229.3250407954</v>
+        <v>590248</v>
       </c>
       <c r="R19" t="n">
-        <v>6701157.805683347</v>
+        <v>6701340</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,19 +2574,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,15 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104520894</v>
+        <v>104520890</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590256.2677711482</v>
+        <v>590224</v>
       </c>
       <c r="R20" t="n">
-        <v>6701347.116733247</v>
+        <v>6701349</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2849,19 +2671,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,15 +2700,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104520926</v>
+        <v>104520891</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590225.9940006013</v>
+        <v>590244</v>
       </c>
       <c r="R21" t="n">
-        <v>6701112.783478609</v>
+        <v>6701331</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,19 +2768,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,15 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104520917</v>
+        <v>104520892</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,10 +2832,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590278.5661941993</v>
+        <v>590267</v>
       </c>
       <c r="R22" t="n">
-        <v>6701385.201479783</v>
+        <v>6701345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,19 +2865,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3112,15 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104520896</v>
+        <v>104520893</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590263.1838432236</v>
+        <v>590260</v>
       </c>
       <c r="R23" t="n">
-        <v>6701407.039472332</v>
+        <v>6701342</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3185,19 +2962,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3224,15 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104520931</v>
+        <v>104520894</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,10 +3026,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590298.5299853174</v>
+        <v>590256</v>
       </c>
       <c r="R24" t="n">
-        <v>6701139.775724018</v>
+        <v>6701347</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3297,19 +3059,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3336,15 +3088,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104520924</v>
+        <v>104520895</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,10 +3123,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590311.9608514119</v>
+        <v>590263</v>
       </c>
       <c r="R25" t="n">
-        <v>6701116.899891712</v>
+        <v>6701346</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3409,19 +3156,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,15 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104520937</v>
+        <v>104520896</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590288.5447983175</v>
+        <v>590263</v>
       </c>
       <c r="R26" t="n">
-        <v>6701143.477671108</v>
+        <v>6701407</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3521,19 +3253,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3560,15 +3282,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104520885</v>
+        <v>104520897</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,10 +3317,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590171.8934813899</v>
+        <v>590245</v>
       </c>
       <c r="R27" t="n">
-        <v>6701299.091888171</v>
+        <v>6701410</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3633,19 +3350,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3672,15 +3379,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104520893</v>
+        <v>104520898</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,10 +3414,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590260.3451851051</v>
+        <v>590259</v>
       </c>
       <c r="R28" t="n">
-        <v>6701342.28017882</v>
+        <v>6701416</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3745,19 +3447,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3784,15 +3476,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104520936</v>
+        <v>104520899</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,10 +3511,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590304.0267430888</v>
+        <v>590266</v>
       </c>
       <c r="R29" t="n">
-        <v>6701117.689885823</v>
+        <v>6701406</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3857,19 +3544,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3896,15 +3573,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104520934</v>
+        <v>104520900</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,10 +3608,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590330.1701784235</v>
+        <v>590250</v>
       </c>
       <c r="R30" t="n">
-        <v>6701160.317622421</v>
+        <v>6701349</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3969,19 +3641,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4008,15 +3670,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104520909</v>
+        <v>104520901</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,10 +3705,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590322.2644234388</v>
+        <v>590231</v>
       </c>
       <c r="R31" t="n">
-        <v>6701398.141592558</v>
+        <v>6701328</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4081,19 +3738,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4120,15 +3767,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104520901</v>
+        <v>104520902</v>
       </c>
       <c r="B32" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,10 +3802,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590231.5246953166</v>
+        <v>590251</v>
       </c>
       <c r="R32" t="n">
-        <v>6701327.735798758</v>
+        <v>6701355</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4193,19 +3835,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4232,15 +3864,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104520887</v>
+        <v>104520904</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,10 +3899,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590237.4093285361</v>
+        <v>590252</v>
       </c>
       <c r="R33" t="n">
-        <v>6701170.846644169</v>
+        <v>6701351</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4305,19 +3932,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4344,15 +3961,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104520913</v>
+        <v>104520905</v>
       </c>
       <c r="B34" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,10 +3996,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590269.2428350718</v>
+        <v>590324</v>
       </c>
       <c r="R34" t="n">
-        <v>6701342.501787398</v>
+        <v>6701411</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4417,19 +4029,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4456,15 +4058,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104520914</v>
+        <v>104520906</v>
       </c>
       <c r="B35" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,10 +4093,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590261.9045443527</v>
+        <v>590321</v>
       </c>
       <c r="R35" t="n">
-        <v>6701359.108531868</v>
+        <v>6701406</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4529,19 +4126,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,15 +4155,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104520929</v>
+        <v>104520907</v>
       </c>
       <c r="B36" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,10 +4190,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>590254.6441901397</v>
+        <v>590315</v>
       </c>
       <c r="R36" t="n">
-        <v>6701134.238079592</v>
+        <v>6701425</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4641,19 +4223,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4680,15 +4252,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104520881</v>
+        <v>104520908</v>
       </c>
       <c r="B37" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590163.477151919</v>
+        <v>590334</v>
       </c>
       <c r="R37" t="n">
-        <v>6701219.871148812</v>
+        <v>6701420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4753,19 +4320,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4792,15 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104520906</v>
+        <v>104520909</v>
       </c>
       <c r="B38" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,10 +4384,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>590321.573329318</v>
+        <v>590323</v>
       </c>
       <c r="R38" t="n">
-        <v>6701406.025213696</v>
+        <v>6701398</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4865,19 +4417,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4904,15 +4446,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104520904</v>
+        <v>104520910</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,10 +4481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>590252.2149474439</v>
+        <v>590304</v>
       </c>
       <c r="R39" t="n">
-        <v>6701350.966279305</v>
+        <v>6701373</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4977,19 +4514,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5016,15 +4543,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104520912</v>
+        <v>104520911</v>
       </c>
       <c r="B40" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>590320.4617279118</v>
+        <v>590321</v>
       </c>
       <c r="R40" t="n">
-        <v>6701410.935529212</v>
+        <v>6701399</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5089,19 +4611,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5128,15 +4640,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>104520886</v>
+        <v>104520912</v>
       </c>
       <c r="B41" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,10 +4675,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590159.6608053438</v>
+        <v>590320</v>
       </c>
       <c r="R41" t="n">
-        <v>6701234.097143658</v>
+        <v>6701411</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5201,19 +4708,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5240,15 +4737,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>104520910</v>
+        <v>104520913</v>
       </c>
       <c r="B42" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,10 +4772,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>590303.613607584</v>
+        <v>590269</v>
       </c>
       <c r="R42" t="n">
-        <v>6701372.492756513</v>
+        <v>6701342</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5313,19 +4805,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5352,15 +4834,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>104520915</v>
+        <v>104520914</v>
       </c>
       <c r="B43" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,10 +4869,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>590267.3393301424</v>
+        <v>590262</v>
       </c>
       <c r="R43" t="n">
-        <v>6701339.491512027</v>
+        <v>6701359</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5425,19 +4902,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5464,15 +4931,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>104520923</v>
+        <v>104520915</v>
       </c>
       <c r="B44" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,10 +4966,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>590254.4721328735</v>
+        <v>590267</v>
       </c>
       <c r="R44" t="n">
-        <v>6701141.147528992</v>
+        <v>6701339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5537,19 +4999,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5576,15 +5028,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104520895</v>
+        <v>104520916</v>
       </c>
       <c r="B45" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,10 +5063,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>590263.2127387247</v>
+        <v>590270</v>
       </c>
       <c r="R45" t="n">
-        <v>6701346.302078418</v>
+        <v>6701341</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5649,19 +5096,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5688,15 +5125,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104520927</v>
+        <v>104520917</v>
       </c>
       <c r="B46" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,10 +5160,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>590236.6238467728</v>
+        <v>590279</v>
       </c>
       <c r="R46" t="n">
-        <v>6701122.924923002</v>
+        <v>6701385</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5761,19 +5193,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5800,15 +5222,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104520900</v>
+        <v>104520918</v>
       </c>
       <c r="B47" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,10 +5257,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>590250.2868544359</v>
+        <v>590279</v>
       </c>
       <c r="R47" t="n">
-        <v>6701348.943027169</v>
+        <v>6701393</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5873,19 +5290,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5912,15 +5319,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104520888</v>
+        <v>104520919</v>
       </c>
       <c r="B48" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,10 +5354,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>590253.2008525791</v>
+        <v>590277</v>
       </c>
       <c r="R48" t="n">
-        <v>6701331.238409691</v>
+        <v>6701357</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5985,19 +5387,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6024,15 +5416,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104520890</v>
+        <v>104520920</v>
       </c>
       <c r="B49" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,10 +5451,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>590224.0759791456</v>
+        <v>590277</v>
       </c>
       <c r="R49" t="n">
-        <v>6701348.784215685</v>
+        <v>6701380</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6097,19 +5484,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6136,15 +5513,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104520889</v>
+        <v>104520922</v>
       </c>
       <c r="B50" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,10 +5548,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>590248.0364938675</v>
+        <v>590241</v>
       </c>
       <c r="R50" t="n">
-        <v>6701339.998407381</v>
+        <v>6701141</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6209,19 +5581,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6248,15 +5610,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>104520930</v>
+        <v>104520923</v>
       </c>
       <c r="B51" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,10 +5645,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>590241.1069771636</v>
+        <v>590255</v>
       </c>
       <c r="R51" t="n">
-        <v>6701101.801357991</v>
+        <v>6701141</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6321,19 +5678,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6360,15 +5707,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104520905</v>
+        <v>104520924</v>
       </c>
       <c r="B52" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,10 +5742,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590324.4161646611</v>
+        <v>590312</v>
       </c>
       <c r="R52" t="n">
-        <v>6701411.034085415</v>
+        <v>6701117</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6433,19 +5775,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6472,15 +5804,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104520922</v>
+        <v>104520925</v>
       </c>
       <c r="B53" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,10 +5839,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>590240.6305753059</v>
+        <v>590288</v>
       </c>
       <c r="R53" t="n">
-        <v>6701140.80287656</v>
+        <v>6701111</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6545,19 +5872,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6584,15 +5901,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104520884</v>
+        <v>104520926</v>
       </c>
       <c r="B54" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,10 +5936,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590175.8080502596</v>
+        <v>590226</v>
       </c>
       <c r="R54" t="n">
-        <v>6701280.918062502</v>
+        <v>6701113</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6657,19 +5969,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6696,15 +5998,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>104520898</v>
+        <v>104520927</v>
       </c>
       <c r="B55" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,10 +6033,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590259.4901826316</v>
+        <v>590237</v>
       </c>
       <c r="R55" t="n">
-        <v>6701416.329697422</v>
+        <v>6701123</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6769,19 +6066,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6808,15 +6095,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>104520882</v>
+        <v>104520929</v>
       </c>
       <c r="B56" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,10 +6130,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590238.4934706129</v>
+        <v>590255</v>
       </c>
       <c r="R56" t="n">
-        <v>6701147.169550829</v>
+        <v>6701134</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6881,19 +6163,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6920,15 +6192,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104520891</v>
+        <v>104520930</v>
       </c>
       <c r="B57" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6960,10 +6227,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590243.3145444395</v>
+        <v>590241</v>
       </c>
       <c r="R57" t="n">
-        <v>6701330.992223296</v>
+        <v>6701102</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6993,19 +6260,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7032,15 +6289,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104520897</v>
+        <v>104520931</v>
       </c>
       <c r="B58" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,10 +6324,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>590244.3142288581</v>
+        <v>590299</v>
       </c>
       <c r="R58" t="n">
-        <v>6701410.02615386</v>
+        <v>6701140</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7105,19 +6357,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7144,15 +6386,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>104520935</v>
+        <v>104520932</v>
       </c>
       <c r="B59" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7184,10 +6421,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>590289.9023181334</v>
+        <v>590295</v>
       </c>
       <c r="R59" t="n">
-        <v>6701128.696329834</v>
+        <v>6701147</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7217,19 +6454,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7256,15 +6483,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>104520932</v>
+        <v>104520933</v>
       </c>
       <c r="B60" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7296,10 +6518,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>590294.4031193145</v>
+        <v>590283</v>
       </c>
       <c r="R60" t="n">
-        <v>6701146.5866381</v>
+        <v>6701242</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7329,19 +6551,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7368,15 +6580,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>104520919</v>
+        <v>104520934</v>
       </c>
       <c r="B61" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7408,10 +6615,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>590276.7830642326</v>
+        <v>590330</v>
       </c>
       <c r="R61" t="n">
-        <v>6701357.503889951</v>
+        <v>6701160</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7441,19 +6648,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7480,15 +6677,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>104520933</v>
+        <v>104520935</v>
       </c>
       <c r="B62" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7520,10 +6712,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>590283.602001261</v>
+        <v>590290</v>
       </c>
       <c r="R62" t="n">
-        <v>6701242.614548266</v>
+        <v>6701128</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7553,19 +6745,9 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7592,10 +6774,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>102234570</v>
+        <v>104520936</v>
       </c>
       <c r="B63" t="n">
-        <v>99032</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7620,36 +6802,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gammelstillavägen, Hofors, Gstr</t>
+          <t>Skoludden Gammelstilla, Gstr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>590266</v>
+        <v>590304</v>
       </c>
       <c r="R63" t="n">
-        <v>6701345</v>
+        <v>6701118</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7673,22 +6839,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>16:34</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>16:34</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7697,22 +6853,215 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>104520937</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skoludden Gammelstilla, Gstr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>590289</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6701144</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>104520939</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skoludden Gammelstilla, Gstr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>590285</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6701131</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54828-2021 artfynd.xlsx
+++ b/artfynd/A 54828-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102233567</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102233679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102233770</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102233902</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102233961</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1389,6 +1419,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102234449</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1513,6 +1548,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102234570</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1630,6 +1670,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102234626</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1727,6 +1772,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520880</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1824,6 +1874,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520881</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1921,6 +1976,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520882</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2018,6 +2078,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520883</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520884</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520885</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2309,6 +2384,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520886</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2406,6 +2486,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520887</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2503,6 +2588,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520888</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2600,6 +2690,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520889</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2697,6 +2792,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520890</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2794,6 +2894,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520891</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2891,6 +2996,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520892</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2988,6 +3098,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520893</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3085,6 +3200,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520894</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3182,6 +3302,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520895</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3279,6 +3404,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520896</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3376,6 +3506,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520897</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3473,6 +3608,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520898</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3570,6 +3710,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520899</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3667,6 +3812,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520900</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3764,6 +3914,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520901</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3861,6 +4016,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520902</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3958,6 +4118,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520904</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4055,6 +4220,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520905</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4152,6 +4322,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520906</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4249,6 +4424,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520907</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4346,6 +4526,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520908</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4443,6 +4628,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520909</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4540,6 +4730,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520910</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4637,6 +4832,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520911</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4734,6 +4934,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520912</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4831,6 +5036,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520913</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4928,6 +5138,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520914</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5025,6 +5240,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520915</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5122,6 +5342,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520916</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5219,6 +5444,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520917</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5316,6 +5546,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520918</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5413,6 +5648,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520919</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5510,6 +5750,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520920</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5607,6 +5852,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520922</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5704,6 +5954,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520923</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5801,6 +6056,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520924</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5898,6 +6158,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520925</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5995,6 +6260,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520926</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6092,6 +6362,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520927</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6189,6 +6464,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520929</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6286,6 +6566,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520930</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6383,6 +6668,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520931</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6480,6 +6770,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520932</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6577,6 +6872,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520933</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6674,6 +6974,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520934</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6771,6 +7076,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520935</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6868,6 +7178,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520936</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6965,6 +7280,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520937</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7062,8 +7382,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104520939</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>